--- a/Sample_run/1/student/KienTTHE186727/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/KienTTHE186727/TC6/GradeDetail.xlsx
@@ -1107,7 +1107,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1166,7 +1166,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1219,7 +1219,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1275,7 +1275,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1334,7 +1334,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1723,7 +1723,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>48024</x:v>
+        <x:v>41720</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1782,7 +1782,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>48024</x:v>
+        <x:v>41720</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>48024</x:v>
+        <x:v>41720</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1891,7 +1891,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>48024</x:v>
+        <x:v>41720</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1950,7 +1950,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>48024</x:v>
+        <x:v>41720</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P24" s="0">
-        <x:v>35884</x:v>
+        <x:v>33668</x:v>
       </x:c>
       <x:c r="Q24" s="0">
         <x:v>4000</x:v>
@@ -2398,7 +2398,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q25" s="0">
-        <x:v>35884</x:v>
+        <x:v>33668</x:v>
       </x:c>
       <x:c r="R25" s="4" t="s">
         <x:v>65</x:v>
@@ -2451,7 +2451,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P26" s="0">
-        <x:v>35884</x:v>
+        <x:v>33668</x:v>
       </x:c>
       <x:c r="Q26" s="0">
         <x:v>4000</x:v>
@@ -2462,7 +2462,7 @@
     </x:row>
     <x:row r="27" spans="1:18">
       <x:c r="A27" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>63</x:v>
@@ -2507,7 +2507,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P27" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="Q27" s="0">
         <x:v>4000</x:v>
@@ -2518,7 +2518,7 @@
     </x:row>
     <x:row r="28" spans="1:18">
       <x:c r="A28" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>63</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q28" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="R28" s="4" t="s">
         <x:v>65</x:v>
@@ -2574,7 +2574,7 @@
     </x:row>
     <x:row r="29" spans="1:18">
       <x:c r="A29" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>63</x:v>
@@ -2619,7 +2619,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="0">
-        <x:v>54256</x:v>
+        <x:v>45444</x:v>
       </x:c>
       <x:c r="Q29" s="0">
         <x:v>4000</x:v>
